--- a/tymczasowe dane/obliczenia temlate.xlsx
+++ b/tymczasowe dane/obliczenia temlate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\Git repozitories\Convection Parameters Calculator\Convection-parameters-calculator\tymczasowe dane\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A86288C-B821-4BFE-934E-E88CDAF930FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C268A224-33A8-4DE0-95AE-717108E07027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -24,9 +24,136 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+  <si>
+    <t>1) Stability of the atmosphere</t>
+  </si>
+  <si>
+    <t>1) temperatura otoczenia</t>
+  </si>
+  <si>
+    <t>Użytkownik podaje dwie wartości:</t>
+  </si>
+  <si>
+    <t>2) temperatura parceli powietrza</t>
+  </si>
+  <si>
+    <t>2) Updraft Strenght</t>
+  </si>
+  <si>
+    <t>Wartość Cape'a</t>
+  </si>
+  <si>
+    <t>Użytkownik podaje jedną wartość: [J/kg]</t>
+  </si>
+  <si>
+    <t>Użytkownik podaje dwie wartości: [stopnie C lub K]</t>
+  </si>
+  <si>
+    <t>3) Vertical velocity</t>
+  </si>
+  <si>
+    <t>Wartość Cin'a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3) Energy Helicy Indec </t>
+  </si>
+  <si>
+    <t>1) Wartość Cape'a [J/kg]</t>
+  </si>
+  <si>
+    <r>
+      <t>2) Skrętność wiatru [m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/s</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <t>4) Derecho Composite Parameter</t>
+  </si>
+  <si>
+    <t>Użytkownik podaje n wartości:</t>
+  </si>
+  <si>
+    <t>1) DCAPE [J/kg]</t>
+  </si>
+  <si>
+    <t>2) MUCAE [J/kg]</t>
+  </si>
+  <si>
+    <t>3) 0-6km shear [kt]</t>
+  </si>
+  <si>
+    <t>4) 0-6hm mean wind [kt]</t>
+  </si>
+  <si>
+    <t>/ 20kt</t>
+  </si>
+  <si>
+    <t>/ 16kt</t>
+  </si>
+  <si>
+    <t>5) Lifting Condensation Level</t>
+  </si>
+  <si>
+    <t>Użytkownik podaje 2 wartości: (w stopniach C!)</t>
+  </si>
+  <si>
+    <t>temperatura i temparatura punktu rosy</t>
+  </si>
+  <si>
+    <t>5) Td</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -34,16 +161,104 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="10"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="7"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF92D050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,14 +266,56 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Dane wejściowe" xfId="1" builtinId="20"/>
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -72,6 +329,275 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>24781</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>2</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>585439</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>168144</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Obraz 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4437C09-DBCB-81E4-FE54-CB55DEC8587A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="635001" y="2375831"/>
+          <a:ext cx="1781097" cy="533654"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3098</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>27877</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1250260</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>136292</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Obraz 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21112209-B8CC-55DE-C834-A5B21964D9DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="613318" y="758901"/>
+          <a:ext cx="2467601" cy="291171"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>40267</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>12389</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>767509</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>6194</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Obraz 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E031947-D8F0-9F0E-50CC-8B94A42B42E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="650487" y="3850267"/>
+          <a:ext cx="1947681" cy="542073"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2089</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>3096</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1102731</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>165239</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Obraz 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{326DEA4E-1A92-90AD-0D78-206EC2BE568A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="612309" y="5303023"/>
+          <a:ext cx="2321081" cy="893167"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9292</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>49560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>58855</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>112011</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Obraz 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9D52FEE-6AD7-B244-2344-437910998B2B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="619512" y="7359804"/>
+          <a:ext cx="4680416" cy="427963"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5041</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>4180</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>167268</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Obraz 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6DF729E-06DC-E625-114A-5E476F5419CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="615261" y="9868830"/>
+          <a:ext cx="4019773" cy="1812072"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -337,9 +863,250 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="B3:E68"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="4" max="4" width="22.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B17" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B25" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B26" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B37" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B44" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B45" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B47" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B48" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B53" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B54" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B67:D68"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B51:D52"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B39:D40"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B20:D21"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B28:D29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D13"/>
+    <mergeCell ref="B17:D17"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>